--- a/survey_templates/027_internal_communication_strategy_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/027_internal_communication_strategy_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -769,8 +769,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'emails',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Emails', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'intranet',_'label':_'intranet'}</t>
+          <t>intranet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Intranet', 'label': 'Intranet'}</t>
+          <t>Intranet</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mobile_app',_'label':_'mobile_app'}</t>
+          <t>mobile_app</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mobile App', 'label': 'Mobile App'}</t>
+          <t>Mobile App</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'meetings',_'label':_'meetings'}</t>
+          <t>meetings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Meetings', 'label': 'Meetings'}</t>
+          <t>Meetings</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_effective',_'label':_'very_effective'}</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Effective', 'label': 'Very Effective'}</t>
+          <t>Very Effective</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_effective',_'label':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Somewhat Effective', 'label': 'Somewhat Effective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_very_effective',_'label':_'not_very_effective'}</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Very Effective', 'label': 'Not Very Effective'}</t>
+          <t>Not Very Effective</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'not_at_all_effective',_'label':_'not_at_all_effective'}</t>
+          <t>not_at_all_effective</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Not at All Effective', 'label': 'Not at All Effective'}</t>
+          <t>Not at All Effective</t>
         </is>
       </c>
     </row>
